--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487723_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487723_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.3084</v>
+        <v>6.6316</v>
       </c>
       <c r="E2" t="n">
-        <v>5.146</v>
+        <v>4.3056</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1624</v>
+        <v>2.3259</v>
       </c>
       <c r="G2" t="n">
         <v>4.9854</v>
@@ -610,13 +610,13 @@
         <v>3.8806</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3349</v>
+        <v>0.6581</v>
       </c>
       <c r="T2" t="n">
-        <v>1.919</v>
+        <v>1.0786</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5841</v>
+        <v>-0.4206</v>
       </c>
       <c r="V2" t="n">
         <v>-0.5642</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. ATIENZA PEREA</t>
+          <t>G. DIAZ MONTERO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.2899</v>
+        <v>6.068</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2598</v>
+        <v>6.191</v>
       </c>
       <c r="F3" t="n">
-        <v>3.0301</v>
+        <v>-0.1231</v>
       </c>
       <c r="G3" t="n">
-        <v>3.3305</v>
+        <v>3.2196</v>
       </c>
       <c r="H3" t="n">
-        <v>2.072</v>
+        <v>-0.9334</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2585</v>
+        <v>4.1531</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9149</v>
+        <v>4.5179</v>
       </c>
       <c r="K3" t="n">
-        <v>2.1792</v>
+        <v>0.0701</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7358</v>
+        <v>4.4479</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4156</v>
+        <v>-1.2983</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1071</v>
+        <v>-1.0035</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5227000000000001</v>
+        <v>-0.2948</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.7761</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.3284</v>
+        <v>-2.1344</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3284</v>
+        <v>2.9105</v>
       </c>
       <c r="S3" t="n">
-        <v>2.3474</v>
+        <v>0.2364</v>
       </c>
       <c r="T3" t="n">
-        <v>2.3912</v>
+        <v>0.4657</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0437</v>
+        <v>-0.2293</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6119</v>
+        <v>1.8358</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2821</v>
+        <v>3.3418</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3299</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. DIAZ MONTERO</t>
+          <t>J. ATIENZA PEREA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.7522</v>
+        <v>5.0854</v>
       </c>
       <c r="E4" t="n">
-        <v>5.63</v>
+        <v>1.919</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1222</v>
+        <v>3.1664</v>
       </c>
       <c r="G4" t="n">
-        <v>3.2196</v>
+        <v>3.3305</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9334</v>
+        <v>2.072</v>
       </c>
       <c r="I4" t="n">
-        <v>4.1531</v>
+        <v>1.2585</v>
       </c>
       <c r="J4" t="n">
-        <v>4.5179</v>
+        <v>2.9149</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0701</v>
+        <v>2.1792</v>
       </c>
       <c r="L4" t="n">
-        <v>4.4479</v>
+        <v>0.7358</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2983</v>
+        <v>0.4156</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0035</v>
+        <v>-0.1071</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2948</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7761</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.1344</v>
+        <v>-2.3284</v>
       </c>
       <c r="R4" t="n">
-        <v>2.9105</v>
+        <v>2.3284</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0794</v>
+        <v>1.1429</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0954</v>
+        <v>1.0503</v>
       </c>
       <c r="U4" t="n">
-        <v>0.016</v>
+        <v>0.0926</v>
       </c>
       <c r="V4" t="n">
-        <v>1.8358</v>
+        <v>0.6119</v>
       </c>
       <c r="W4" t="n">
-        <v>3.3418</v>
+        <v>0.2821</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.506</v>
+        <v>0.3299</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. GONZALEZ  LONGARELA</t>
+          <t>J. DOMINGUEZ LARRE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4818</v>
+        <v>0.128</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.2994</v>
+        <v>-1.0219</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8176</v>
+        <v>1.1498</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4399</v>
+        <v>-1.0555</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.7762</v>
+        <v>-0.4861</v>
       </c>
       <c r="I5" t="n">
-        <v>2.2161</v>
+        <v>-0.5694</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.4658</v>
+        <v>-0.7806999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.8866</v>
+        <v>0.4449</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4209</v>
+        <v>-1.2256</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9056</v>
+        <v>-0.2748</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1104</v>
+        <v>-0.931</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7952</v>
+        <v>0.6562</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.1642</v>
+        <v>2.5224</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9105</v>
+        <v>-0.5821</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7463</v>
+        <v>3.1045</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2425</v>
+        <v>0.4969</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5709</v>
+        <v>0.3409</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3284</v>
+        <v>0.1559</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-1.8358</v>
       </c>
       <c r="W5" t="n">
-        <v>1.506</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.506</v>
+        <v>-1.8358</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. LARDIES GUILLEN</t>
+          <t>D. GONZALEZ  LONGARELA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5714</v>
+        <v>-0.018</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1282</v>
+        <v>-0.9991</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5568</v>
+        <v>0.9811</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.1809</v>
+        <v>0.4399</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.7367</v>
+        <v>-1.7762</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.4442</v>
+        <v>2.2161</v>
       </c>
       <c r="J6" t="n">
-        <v>-3.2137</v>
+        <v>-0.4658</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.9196</v>
+        <v>-1.8866</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.2941</v>
+        <v>1.4209</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0327</v>
+        <v>0.9056</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1829</v>
+        <v>0.1104</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1502</v>
+        <v>0.7952</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3881</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.3582</v>
+        <v>-2.9105</v>
       </c>
       <c r="R6" t="n">
         <v>1.7463</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2797</v>
+        <v>0.7063</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9959</v>
+        <v>0.8712</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2838</v>
+        <v>-0.1649</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9418</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.4477</v>
+        <v>1.506</v>
       </c>
       <c r="X6" t="n">
         <v>-1.506</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. DOMINGUEZ LARRE</t>
+          <t>J. DE DOMINGO GARAY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6244</v>
+        <v>-1.054</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.8832</v>
+        <v>-0.97</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2589</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.0555</v>
+        <v>0.2037</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4861</v>
+        <v>0.0297</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5694</v>
+        <v>0.1741</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.7806999999999999</v>
+        <v>0.0818</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4449</v>
+        <v>0.0412</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.2256</v>
+        <v>0.0406</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2748</v>
+        <v>0.1219</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.931</v>
+        <v>-0.0115</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6562</v>
+        <v>0.1335</v>
       </c>
       <c r="P7" t="n">
-        <v>2.5224</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.5821</v>
+        <v>-0.9702</v>
       </c>
       <c r="R7" t="n">
-        <v>3.1045</v>
+        <v>0.5821</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2555</v>
+        <v>-0.2577</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5204</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2649</v>
+        <v>-0.1761</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.8358</v>
+        <v>-0.6119</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.8358</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. DE DOMINGO GARAY</t>
+          <t>G. LARDIES GUILLEN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2086</v>
+        <v>-1.1476</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0701</v>
+        <v>-1.5681</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1385</v>
+        <v>0.4206</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2037</v>
+        <v>-3.1809</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0297</v>
+        <v>-1.7367</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1741</v>
+        <v>-1.4442</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0818</v>
+        <v>-3.2137</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0412</v>
+        <v>-1.9196</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0406</v>
+        <v>-1.2941</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1219</v>
+        <v>0.0327</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0115</v>
+        <v>0.1829</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1335</v>
+        <v>-0.1502</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3881</v>
+        <v>0.3881</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9702</v>
+        <v>-1.3582</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5821</v>
+        <v>1.7463</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4123</v>
+        <v>0.7035</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1817</v>
+        <v>0.556</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2306</v>
+        <v>0.1475</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6119</v>
+        <v>0.9418</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.4477</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6119</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4004</v>
+        <v>-1.3548</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6254999999999999</v>
+        <v>-0.5254</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7749</v>
+        <v>-0.8294</v>
       </c>
       <c r="G9" t="n">
         <v>-0.788</v>
@@ -1156,13 +1156,13 @@
         <v>0.194</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1945</v>
+        <v>-0.1489</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0606</v>
+        <v>0.0395</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1339</v>
+        <v>-0.1884</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6119</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. LARDIES GUILLEN</t>
+          <t>H. PEREZ SANCHEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6102</v>
+        <v>-2.1353</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.3329</v>
+        <v>-2.1853</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7227</v>
+        <v>0.0499</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.2151</v>
+        <v>-1.3839</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.9748</v>
+        <v>-0.201</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7597</v>
+        <v>-1.1829</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6411</v>
+        <v>-0.3548</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.2729</v>
+        <v>-0.3954</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6318</v>
+        <v>0.0406</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.574</v>
+        <v>-1.029</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7019</v>
+        <v>0.1944</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1279</v>
+        <v>-1.2235</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.3582</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.3284</v>
+        <v>-1.9403</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9702</v>
+        <v>1.1642</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0368</v>
+        <v>0.0247</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3634</v>
+        <v>0.1099</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3266</v>
+        <v>-0.0852</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>H. PEREZ SANCHEZ</t>
+          <t>R. LARDIES GUILLEN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6448</v>
+        <v>-2.6191</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5857</v>
+        <v>-3.2328</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0591</v>
+        <v>0.6137</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.3839</v>
+        <v>-1.2151</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.201</v>
+        <v>-1.9748</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.1829</v>
+        <v>0.7597</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3548</v>
+        <v>-0.6411</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3954</v>
+        <v>-1.2729</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0406</v>
+        <v>0.6318</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.029</v>
+        <v>-0.574</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1944</v>
+        <v>-0.7019</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.2235</v>
+        <v>0.1279</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.7761</v>
+        <v>-1.3582</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9403</v>
+        <v>-2.3284</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1642</v>
+        <v>0.9702</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4847</v>
+        <v>-0.0457</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2905</v>
+        <v>-0.2633</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1943</v>
+        <v>0.2176</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9748</v>
+        <v>-2.9381</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.251</v>
+        <v>-2.0508</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7238</v>
+        <v>-0.8873</v>
       </c>
       <c r="G12" t="n">
         <v>-0.8718</v>
@@ -1390,13 +1390,13 @@
         <v>2.3284</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4612</v>
+        <v>-0.4245</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6539</v>
+        <v>-0.4537</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1927</v>
+        <v>0.0292</v>
       </c>
       <c r="V12" t="n">
         <v>-1.8358</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.2771</v>
+        <v>-3.786</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.9224</v>
+        <v>-1.6221</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.3547</v>
+        <v>-2.1639</v>
       </c>
       <c r="G13" t="n">
         <v>-3.2955</v>
@@ -1468,13 +1468,13 @@
         <v>1.3582</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.3398</v>
+        <v>-0.8488</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6662</v>
+        <v>-0.3659</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6736</v>
+        <v>-0.4828</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6119</v>
@@ -1501,28 +1501,28 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.557000000000001</v>
+        <v>2.860099999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.062600000000002</v>
+        <v>-1.759899999999999</v>
       </c>
       <c r="F14" t="n">
         <v>4.6197</v>
       </c>
       <c r="G14" t="n">
-        <v>0.388399999999999</v>
+        <v>0.3884000000000016</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.701000000000001</v>
+        <v>-5.701</v>
       </c>
       <c r="I14" t="n">
-        <v>6.089600000000002</v>
+        <v>6.0896</v>
       </c>
       <c r="J14" t="n">
-        <v>6.718200000000002</v>
+        <v>6.718199999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.2055999999999996</v>
+        <v>-0.2055999999999992</v>
       </c>
       <c r="L14" t="n">
         <v>6.9241</v>
@@ -1534,10 +1534,10 @@
         <v>-5.4953</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.8344000000000004</v>
+        <v>-0.8343999999999998</v>
       </c>
       <c r="P14" t="n">
-        <v>2.9105</v>
+        <v>2.910500000000001</v>
       </c>
       <c r="Q14" t="n">
         <v>-19.4034</v>
@@ -1546,13 +1546,13 @@
         <v>22.3137</v>
       </c>
       <c r="S14" t="n">
-        <v>1.940299999999999</v>
+        <v>2.2432</v>
       </c>
       <c r="T14" t="n">
-        <v>3.0449</v>
+        <v>3.3476</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.1046</v>
+        <v>-1.1045</v>
       </c>
       <c r="V14" t="n">
         <v>-2.682</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0421</v>
+        <v>4.4176</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1008</v>
+        <v>2.8005</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9413</v>
+        <v>1.6171</v>
       </c>
       <c r="G15" t="n">
         <v>4.1111</v>
@@ -1624,13 +1624,13 @@
         <v>2.7164</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5629999999999999</v>
+        <v>-0.1876</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4385</v>
+        <v>0.1382</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.0015</v>
+        <v>-0.3258</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2821</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.7858</v>
+        <v>3.9493</v>
       </c>
       <c r="E16" t="n">
-        <v>4.1776</v>
+        <v>3.7772</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3918</v>
+        <v>0.1721</v>
       </c>
       <c r="G16" t="n">
         <v>0.8332000000000001</v>
@@ -1702,13 +1702,13 @@
         <v>2.7164</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3026</v>
+        <v>-0.1391</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7907</v>
+        <v>0.3903</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.0933</v>
+        <v>-0.5293</v>
       </c>
       <c r="V16" t="n">
         <v>4.6134</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. NIANG</t>
+          <t>D. OJEDA DAVILA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4102</v>
+        <v>-0.3607</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4134</v>
+        <v>-0.3931</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.8235</v>
+        <v>0.0324</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5396</v>
+        <v>-0.5669999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1592</v>
+        <v>0.4712</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6196</v>
+        <v>-1.0383</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9587</v>
+        <v>0.6736</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.0824</v>
       </c>
       <c r="L17" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.419</v>
+        <v>-1.2406</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2817</v>
+        <v>0.3889</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7008</v>
+        <v>-1.6294</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.5523</v>
+        <v>0.194</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.1045</v>
+        <v>-1.1642</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5523</v>
+        <v>1.3582</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3203</v>
+        <v>0.0123</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5473</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.227</v>
+        <v>-0.0852</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>3.0119</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.7298</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5091</v>
+        <v>-0.6604</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.4965</v>
+        <v>-1.6967</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9875</v>
+        <v>1.0364</v>
       </c>
       <c r="G18" t="n">
         <v>-1.5307</v>
@@ -1858,13 +1858,13 @@
         <v>3.4926</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3515</v>
+        <v>0.2002</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2568</v>
+        <v>0.0566</v>
       </c>
       <c r="U18" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.1436</v>
       </c>
       <c r="V18" t="n">
         <v>0.2821</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. GARCÍA PEREZ</t>
+          <t>M. NIANG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8338</v>
+        <v>-0.8068</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1704</v>
+        <v>1.2132</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.0042</v>
+        <v>-2.0199</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6841</v>
+        <v>0.5396</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.678</v>
+        <v>1.1592</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0061</v>
+        <v>-0.6196</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6847</v>
+        <v>0.9587</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0124</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6724</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3689</v>
+        <v>-0.419</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6904</v>
+        <v>0.2817</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6785</v>
+        <v>-0.7008</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1642</v>
+        <v>-1.5523</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-3.1045</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1642</v>
+        <v>1.5523</v>
       </c>
       <c r="S19" t="n">
-        <v>0.522</v>
+        <v>-0.07630000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4856</v>
+        <v>0.3471</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0363</v>
+        <v>-0.4234</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.8358</v>
+        <v>0.2821</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>3.0119</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.8358</v>
+        <v>-2.7298</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. OJEDA DAVILA</t>
+          <t>E. GARCÍA PEREZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0035</v>
+        <v>-0.8794</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7935</v>
+        <v>1.0703</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2101</v>
+        <v>-1.9496</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.5669999999999999</v>
+        <v>-0.6841</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4712</v>
+        <v>-0.678</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0383</v>
+        <v>-0.0061</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6736</v>
+        <v>0.6847</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0824</v>
+        <v>0.0124</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5911999999999999</v>
+        <v>0.6724</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2406</v>
+        <v>-1.3689</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3889</v>
+        <v>-0.6904</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.6294</v>
+        <v>-0.6785</v>
       </c>
       <c r="P20" t="n">
-        <v>0.194</v>
+        <v>1.1642</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1642</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3582</v>
+        <v>1.1642</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6304999999999999</v>
+        <v>0.4764</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3028</v>
+        <v>0.3855</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3277</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.8358</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.8358</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.318</v>
+        <v>-1.0755</v>
       </c>
       <c r="E21" t="n">
         <v>-2.2102</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8923</v>
+        <v>1.1347</v>
       </c>
       <c r="G21" t="n">
         <v>0.0035</v>
@@ -2092,13 +2092,13 @@
         <v>0.9702</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3513</v>
+        <v>-0.1088</v>
       </c>
       <c r="T21" t="n">
         <v>-0.2905</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0608</v>
+        <v>0.1817</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8606</v>
+        <v>-2.0387</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.2353</v>
+        <v>-4.1352</v>
       </c>
       <c r="F22" t="n">
-        <v>2.3747</v>
+        <v>2.0965</v>
       </c>
       <c r="G22" t="n">
         <v>-3.8709</v>
@@ -2170,13 +2170,13 @@
         <v>2.9105</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.4635</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2568</v>
+        <v>0.3569</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3848</v>
+        <v>0.1066</v>
       </c>
       <c r="V22" t="n">
         <v>-0.3776</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.4499</v>
+        <v>-3.1007</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.7464</v>
+        <v>-5.0457</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2965</v>
+        <v>1.945</v>
       </c>
       <c r="G23" t="n">
         <v>0.7769</v>
@@ -2248,13 +2248,13 @@
         <v>2.5224</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.9282</v>
+        <v>-0.579</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0779</v>
+        <v>-0.3772</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8502999999999999</v>
+        <v>-0.2019</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.557200000000001</v>
+        <v>-0.555299999999999</v>
       </c>
       <c r="E24" t="n">
         <v>-4.6197</v>
       </c>
       <c r="F24" t="n">
-        <v>2.0627</v>
+        <v>4.064699999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.3883999999999997</v>
+        <v>-0.3883999999999993</v>
       </c>
       <c r="H24" t="n">
         <v>5.7012</v>
@@ -2305,7 +2305,7 @@
         <v>5.4955</v>
       </c>
       <c r="L24" t="n">
-        <v>0.8345999999999993</v>
+        <v>0.8345999999999998</v>
       </c>
       <c r="M24" t="n">
         <v>-6.7182</v>
@@ -2317,7 +2317,7 @@
         <v>-6.924</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.910500000000001</v>
+        <v>-2.9105</v>
       </c>
       <c r="Q24" t="n">
         <v>-22.3137</v>
@@ -2326,13 +2326,13 @@
         <v>19.4032</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.9402</v>
+        <v>0.0616000000000001</v>
       </c>
       <c r="T24" t="n">
         <v>1.1045</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.0448</v>
+        <v>-1.0429</v>
       </c>
       <c r="V24" t="n">
         <v>2.6821</v>
@@ -2341,7 +2341,7 @@
         <v>10.2597</v>
       </c>
       <c r="X24" t="n">
-        <v>-7.577599999999999</v>
+        <v>-7.5776</v>
       </c>
     </row>
   </sheetData>
